--- a/important_mails_2026-07-17.xlsx
+++ b/important_mails_2026-07-17.xlsx
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KYC审核类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1051,70 +1051,21 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
+          <t>Wed, 15 Jul 2026 14:47:49 +0000</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Know Your Customer (KYC) verification process support</t>
+          <t>Tu pago está en camino</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96
- Pending Know Your Customer (KYC) account verification
- Hello,
- We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
- Submit documentation
- In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
- What happens next?
- Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
- Once the verification is complete, you will receive a performance notification and email advising you of the result.
- We’re here to help.
- If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
- For more informa</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 14:47:49 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1131,39 +1082,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 14:58:09 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1183,39 +1134,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 14:21:36 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1235,39 +1186,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 04:03:58 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1284,39 +1235,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 10:36:54 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1333,39 +1284,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 10:30:59 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1385,39 +1336,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 23:31:39 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1437,10 +1388,61 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to avoid listing deactivation</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Hello Weihai CA,
+ Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
+ For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
+ To avoid further impact to your account, close or delete any non-compliant listings that you do </t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1455,21 +1457,2496 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Fri, 10 Jul 2026 12:07:00 +0000</t>
+          <t>Fri, 10 Jul 2026 15:01:39 +0000</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>完成账户验证以恢复付款</t>
+          <t>Manage VAT &amp; EPR Requirements Directly Within Your Pan-European FBA
+ Inventory Portal</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Visit the Pan-EU Portal to Manage Listings,﻿ Compliance &amp;amp; Expansion in EU
+                                                    ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
+https://go.amazonsellerservices.com/e/229492/2026-07-10/7z4kvj4/6762447069/h/VpEb28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 11:19:50 +0000</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Global Warehousing and Distribution &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Global Warehousing and Distribution’s new China shipping options are live</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Choose Shanghai or Shenzhen with Free on Board support
+ Global Warehousing and Distribution (GWD)
+ GWD now gives you more flexibility in how you ship to US FBA. GWD has expanded to Shanghai, one of China's largest manufacturing and export hubs, and now supports the Free on Board (FOB) incoterm across all its locations.
+ What this means for you:
+- Send to a location closer to your manufacturer: Choose from GWD facilities in Shanghai or Shenzhen to shorten the distance between your manufacturer and GWD, so your inventory is received and ready for US FBA replenishment faster.
+- Keep control of your export documentation: With the FOB incoterm, you can obtain separate invoices for export declaration and origin port handling charges to support your export tax rebate process.
+- Reduce US storage costs: Store bulk inventory with GWD in Shanghai or Shenzhen and move it into US FBA based on demand, so you're not paying US storage fees on inventory that isn't ready to sell.
+- Start small, scale when ready: Send as little as one shipment to GWD, with no long-term commitment and no peak storage fee increases, so you can confirm GWD fits your supply chain before increasing volume.
+ Learn mor</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo]
+We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
+[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-all-ref--xx-invmgr-dnav-xx/7z4njtm/6769022163/h/8vIvt897JI4FIoN1zpbOfGsnK8r65MNsf-5hLns08l0)
+We've improved our Similar Item Pricing tool designed specifically to help you make faster, more informed pricing decisions.
+Here’s what’s new:
+Browse Amazon-highlighted similar products based on your catalog or search for specific products yourself
+Access key data points including Delivery Experience, Prime Status, Product Ratings, and more
+Ready to get started? It's simple:
+- Go to your 'Manage All Inventory'
+- Click on 'View Reference Prices' in the Pricing column
+- Select 'Set Up Similar Products' to access the dashboard
+The Similar Items Dashboard can help you research prices for products customers may see as comparable to yours and make more informed pricing decision.
+[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-al</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Get increased New Selection Program (2026) benefits starting July
+ 30</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
+ Hello,
+ If you’re currently enrolled in our existing New Selection Program , you’ll automatically receive New Selection Program (2026) benefits for new branded FBA ASINs that launch starting July 30, through October 31, 2026, as an introductory offer.
+ To continue to receive New Selection Program (2026) benefits after October 31, you must confirm your enrollment on Enroll in New Selection Program (2026) . From July 30, the existing New Selection Program will end.
+New benefits for an eligible new-to-FBA product include (applicable from first inventory received date):
+- Instant fee credits equivalent to capping referral fees to 10% (or your existing rate, whichever is lower) on your first 100 units and 5% (or your existing rate, whichever is lower) on the next 100 units. Credits apply to major fees, like referral and fulfillment fees.
+- $50 in coupon variable fee credits and $75 in Vine enrollment fee credits (applied to middle tier), usable within the first 60 days.
+- Free storage, free c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Worten Marketplace - Portugal y España</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>¡Buenos días!
+Espero que te encuentres bien.
+Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
+Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
+Sobre Worten.
+Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
+En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
+Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
+Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
+Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
+Worten Marketplace tiene una estrategia B2C, c</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-07-23</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-07-23 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRC8LPGS Quantity: 1
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- lnAMEX0pyh
+ Unsellable Products:
+- FNSKU: X002A05YW5 Quantity: 1
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-07-23</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-07-23 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRC8LPGS Quantity: 2
+- FNSKU: B0DRCB74YN Quantity: 7
+- FNSKU: B0DRCF83VZ Quantity: 10
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal ord</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
+[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
+Sessions matched to your experience level
+The Amazon Accelerate 2026 [session catalog](https://go.amazonsellerservices.com/e/229492/e-5a3b486e4e26-session-catalog/7z4n1pm/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg) is live. Every session is clearly marked by experience level (beginner, intermediate, and advanced) so you can find the right match for where you are. Formats include lightning talks, workshops, roundtables, presentations, panels, fireside chats, and more.
+Join us in person at Amazon Accelerate 2026 from September 22 to 24 in Seattle. Save $100 with early-bird pricing until August 8!
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
+"Attending Amazon Accelerate for the first time has been an amazing experience! I feel inspired and more confide</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Your Accelerate 2026 session catalog is now live</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
+[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
+Approachable formats, actionable takeaways, and proven strategies
+The Amazon Accelerate 2026 [session catalog](https://go.amazonsellerservices.com/e/229492/e-5a3b486e4e26-session-catalog/7z4n1sf/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk) is live. This year's lineup spans 80+ sessions across 11 breakout topics, built for every experience level. Whether you're still finding your footing or ready to take the next step, you'll find content that meets you where you are.
+New for 2026: Expect more interactive sessions, expanded Q&amp;A opportunities, and sessions featuring fellow sellers sharing their real-world strategies.
+Join us in person at Amazon Accelerate 2026 from September 22 to 24 in Seattle. Save $100 with early-bird pricing until August 8!
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3an</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (0uWEj59btv)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6202602-3593025
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1583298414144679</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 3 Jul 2026 09:21:14 +0000</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Jul 2026 09:24:36 +0000</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Jul 2026 04:17:03 +0000</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (go0BbIMUoR)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6026936-3810853
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-193515716027065</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 1 Jul 2026 16:27:45 +0000</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (hbXn1jQJTV)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-0881392-7844068
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1565706782398233</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 1 Jul 2026 05:07:37 +0000</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 08:53:34 +0000</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (j2cKowrwuw)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6586757-6351206
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-510175063560598</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 30 Jun 2026 04:56:23 +0000</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 29 Jun 2026 23:44:37 +0000</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (H7OQM8penQ)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1191815-3214046
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1161086507307943</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 29 Jun 2026 04:56:45 +0000</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID H7OQM8penQ
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 29, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1724036457613526</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Balance paid on your Amazon seller account</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202606281349
+ Was this email helpful?
+ SPC-USAmazon-510175622387886</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 28 Jun 2026 04:47:15 +0000</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 26 Jun 2026 04:59:26 +0000</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 26 Jun 2026 03:07:14 +0000</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (HI24ImSBWG)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-4837972-8437069
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1301823993910502</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 15:41:57 +0000</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID HI24ImSBWG
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 26, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1301823993671780</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 09:07:47 +0000</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF
+Dear Weihai US,
+As a valued Multichannel Fulfilment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than July 2.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_cOSOOyGQjgcTF54?Q_CHL=gl&amp;amp;Q_DL=EMD_7XHD09nVvjxfqAf_cOSOOyGQjgcTF54_CGC_i4S2zEfdL6jRC00&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multichannel Fulfilment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon C</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 04:53:58 +0000</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 25 Jun 2026 00:27:04 +0000</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (FyqS0yVk5B)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 2
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 1
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3320999-8288160
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1987919249117870</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 24 Jun 2026 04:45:26 +0000</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 15:11:41 +0000</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID FyqS0yVk5B
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 24, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-1671259898541181</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 23 Jun 2026 02:24:45 +0000</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (1M28ecQsao)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1410418-0204243
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-404622503407998</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 06:20:20 +0000</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (9U/Ti42WHq)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-8813600-4095116
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-1671259338897621</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 22 Jun 2026 04:45:03 +0000</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 21 Jun 2026 14:27:31 +0000</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID 1M28ecQsao
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 22, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-492583430909528</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 15:35:08 +0000</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (hCxOB8pPpU)</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-0438203-1064657
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-439806876012022</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 15:10:33 +0000</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID hbXn1jQJTV
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 21, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-2163841110748510</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 19 Jun 2026 14:16:06 +0000</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID hCxOB8pPpU
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-193516273769387</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 19 Jun 2026 08:10:33 +0000</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF
+Dear Weihai US,
+As a valued Multichannel Fulfilment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than July 2.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_cOSOOyGQjgcTF54?Q_CHL=gl&amp;amp;Q_DL=EMD_7XHD09nVvjxfqAf_cOSOOyGQjgcTF54_CGC_i4S2zEfdL6jRC00&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multichannel Fulfilment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon C</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 20:47:57 +0000</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (oWLDk2Qx2d)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 2
+Quantity Successfully Destroyed: 2
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-8566067-2437751
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1301823991515480</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 20:39:11 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (Emm3dPMsXA)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 1
+Quantity Successfully Destroyed: 1
+Quantity Cancelled: 0
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-6737416-2398463
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-1600891154547102</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 17:59:35 +0000</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Please share your feedback on MCF
+Dear Weihai EU,
+As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than July 2.
+(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_3LaptS2dCyJQfae?Q_CHL=gl&amp;amp;Q_DL=EMD_G3TZbOh3yA5KUhZ_3LaptS2dCyJQfae_CGC_q2ZHx06yRtKOa12&amp;amp;_g_=g
+This submission form is unique to your Seller account and can only be submitted once.
+DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
+Thank you,
+Your Multichannel Fulfillment Team
+This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 17 Jun 2026 15:48:24 +0000</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID Emm3dPMsXA
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on June 18, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-2040695807881994</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>KYC审核类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Know Your Customer (KYC) verification process support</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Pending Know Your Customer (KYC) account verification
+ Hello,
+ We are conducting a review of your Amazon Payments Account. We need additional information or documents to continue with your account verification. In accordance with regulations, you must complete an account verification process. Please go to the Identity Information page to provide the required information or documents:
+ Submit documentation
+ In some cases, we will send a notification that outlines the details of the request related to your Amazon Payments account. Please check the most recent performance notifications starting with the subject [Action Required]: Performance Notifications .
+ What happens next?
+ Once you have provided the requested information or documents, we will continue with your account verification. Please continue to proactively check the performance notifications or emails to understand if further information or documents are needed from you.
+ Once the verification is complete, you will receive a performance notification and email advising you of the result.
+ We’re here to help.
+ If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
+ For more informa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>KYC审核类</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Seller News: June 2026</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services
+ 96
+ Updates on Prime Day, handling time requirements, Seller Central, and more.
+ Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
+ Get ready for Prime Day: June 23–26
+ Prime Day is back from June 23–26, giving Prime members a head start on the season with deals across top brands they love, trending products, and items exclusive to Amazon. As recently announced, key sourcing dates have been extended, giving you more time to schedule deals, confirm inventory, and plan Prime Exclusive Discounts on eligible selection.
+ Read more .
+ Updates to improve your product titles begin on July 27
+ To ensure your product titles appeal to customers everywhere, we’re making some changes that will help you show your product name and your product highlights seamlessly.
+ Read more .
+ New handling time requirements for seller-fulfilled products
+ Fast and accurate delivery builds customer trust and is a key factor in purchase decisions. In fact, every one day improvement in promised delivery time leads to an average 5% increase in sales. As such, we’re implementing a new handling time requirem</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 10 Jul 2026 12:07:00 +0000</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>完成账户验证以恢复付款</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  完成账户验证以恢复付款
@@ -1512,39 +3989,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:05:39 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Completa la verificación de la cuenta para restaurar los pagos</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verificación de la cuenta para restaurar los pagos
@@ -1561,39 +4038,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:04:08 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Accountverificatie voltooien om vergoedingen te herstellen</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Accountverificatie voltooien om vergoedingen te herstellen
@@ -1610,39 +4087,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:02:02 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Complete account verification to restore disbursements</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Complete account verification to restore disbursements
@@ -1660,39 +4137,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 12:00:06 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Ukończ weryfikację konta, aby przywrócić wypłaty środków</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Ukończ weryfikację konta, aby przywrócić wypłaty środków
@@ -1709,39 +4186,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:59:04 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Slutför kontoverifieringen så att utbetalningarna kan återställas</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför kontoverifieringen så att utbetalningarna kan återställas
@@ -1758,39 +4235,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:57:07 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Completa la verifica dell'account per ripristinare i pagamenti</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Completa la verifica dell'account per ripristinare i pagamenti
@@ -1807,39 +4284,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:55:07 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Complete account verification to restore disbursements</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Complete account verification to restore disbursements
@@ -1857,39 +4334,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:53:42 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Terminez la vérification du compte pour restaurer les versements.</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Terminez la vérification du compte pour restaurer les versements.
@@ -1906,39 +4383,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:44:42 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>完成账户验证以恢复付款</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  完成账户验证以恢复付款
@@ -1981,2483 +4458,6 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 06:06:37 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Hello Weihai CA,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do </t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Jul 2026 15:01:39 +0000</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Manage VAT &amp; EPR Requirements Directly Within Your Pan-European FBA
- Inventory Portal</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Visit the Pan-EU Portal to Manage Listings,﻿ Compliance &amp;amp; Expansion in EU
-                                                    ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­
-https://go.amazonsellerservices.com/e/229492/2026-07-10/7z4kvj4/6762447069/h/VpEb28</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 16 Jul 2026 11:19:50 +0000</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Global Warehousing and Distribution &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Global Warehousing and Distribution’s new China shipping options are live</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>96
- Choose Shanghai or Shenzhen with Free on Board support
- Global Warehousing and Distribution (GWD)
- GWD now gives you more flexibility in how you ship to US FBA. GWD has expanded to Shanghai, one of China's largest manufacturing and export hubs, and now supports the Free on Board (FOB) incoterm across all its locations.
- What this means for you:
-- Send to a location closer to your manufacturer: Choose from GWD facilities in Shanghai or Shenzhen to shorten the distance between your manufacturer and GWD, so your inventory is received and ready for US FBA replenishment faster.
-- Keep control of your export documentation: With the FOB incoterm, you can obtain separate invoices for export declaration and origin port handling charges to support your export tax rebate process.
-- Reduce US storage costs: Store bulk inventory with GWD in Shanghai or Shenzhen and move it into US FBA based on demand, so you're not paying US storage fees on inventory that isn't ready to sell.
-- Start small, scale when ready: Send as little as one shipment to GWD, with no long-term commitment and no peak storage fee increases, so you can confirm GWD fits your supply chain before increasing volume.
- Learn mor</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 12:22:37 +0000</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Introducing the Improved Similar Items Dashboard – Smarter Pricing Starts Now</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo]
-We're excited to announce the launch of the improved Similar Items Dashboard. It helps you understand how comparable products are priced on Amazon. Instead of spending hours on manual research, it provides quick access to Amazon data – all in one place.
-[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-all-ref--xx-invmgr-dnav-xx/7z4njtm/6769022163/h/8vIvt897JI4FIoN1zpbOfGsnK8r65MNsf-5hLns08l0)
-We've improved our Similar Item Pricing tool designed specifically to help you make faster, more informed pricing decisions.
-Here’s what’s new:
-Browse Amazon-highlighted similar products based on your catalog or search for specific products yourself
-Access key data points including Delivery Experience, Prime Status, Product Ratings, and more
-Ready to get started? It's simple:
-- Go to your 'Manage All Inventory'
-- Click on 'View Reference Prices' in the Pricing column
-- Select 'Set Up Similar Products' to access the dashboard
-The Similar Items Dashboard can help you research prices for products customers may see as comparable to yours and make more informed pricing decision.
-[Explore the Dashboard Now](https://go.amazonsellerservices.com/e/229492/tus-al</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 15 Jul 2026 10:17:38 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Get increased New Selection Program (2026) benefits starting July
- 30</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>96
- Effective July 30, 2026, the New Selection Program (2026) launches with increased benefits to help you launch new branded products with reduced costs and complexity while boosting early sales.
- Hello,
- If you’re currently enrolled in our existing New Selection Program , you’ll automatically receive New Selection Program (2026) benefits for new branded FBA ASINs that launch starting July 30, through October 31, 2026, as an introductory offer.
- To continue to receive New Selection Program (2026) benefits after October 31, you must confirm your enrollment on Enroll in New Selection Program (2026) . From July 30, the existing New Selection Program will end.
-New benefits for an eligible new-to-FBA product include (applicable from first inventory received date):
-- Instant fee credits equivalent to capping referral fees to 10% (or your existing rate, whichever is lower) on your first 100 units and 5% (or your existing rate, whichever is lower) on the next 100 units. Credits apply to major fees, like referral and fulfillment fees.
-- $50 in coupon variable fee credits and $75 in Vine enrollment fee credits (applied to middle tier), usable within the first 60 days.
-- Free storage, free c</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 12 Jul 2026 17:10:46 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Luana Camargo &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Luana Camargo y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C, c</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 04:26:29 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-07-23</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-07-23 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRC8LPGS Quantity: 1
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 04:08:56 +0000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- lnAMEX0pyh
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 11 Jul 2026 03:06:39 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-07-23</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-07-23 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRC8LPGS Quantity: 2
-- FNSKU: B0DRCB74YN Quantity: 7
-- FNSKU: B0DRCF83VZ Quantity: 10
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal ord</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 16 Jul 2026 15:32:18 +0000</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Accelerate 2026: Sessions designed for where you are and where you’re going</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1pf/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
-[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
-Sessions matched to your experience level
-The Amazon Accelerate 2026 [session catalog](https://go.amazonsellerservices.com/e/229492/e-5a3b486e4e26-session-catalog/7z4n1pm/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg) is live. Every session is clearly marked by experience level (beginner, intermediate, and advanced) so you can find the right match for where you are. Formats include lightning talks, workshops, roundtables, presentations, panels, fireside chats, and more.
-Join us in person at Amazon Accelerate 2026 from September 22 to 24 in Seattle. Save $100 with early-bird pricing until August 8!
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1pj/6770773185/h/WdBYUGZo6UnxZlR8bvark7SKCv06gleKjoxG039m7cg)
-"Attending Amazon Accelerate for the first time has been an amazing experience! I feel inspired and more confide</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 14 Jul 2026 15:11:01 +0000</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Your Accelerate 2026 session catalog is now live</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-07-14/7z4n1s7/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
-[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk)
-Approachable formats, actionable takeaways, and proven strategies
-The Amazon Accelerate 2026 [session catalog](https://go.amazonsellerservices.com/e/229492/e-5a3b486e4e26-session-catalog/7z4n1sf/6767228964/h/eXAL3anI3dWEgFXK_p_u6QFSTde6SYcFg0MO4Yodnjk) is live. This year's lineup spans 80+ sessions across 11 breakout topics, built for every experience level. Whether you're still finding your footing or ready to take the next step, you'll find content that meets you where you are.
-New for 2026: Expect more interactive sessions, expanded Q&amp;A opportunities, and sessions featuring fellow sellers sharing their real-world strategies.
-Join us in person at Amazon Accelerate 2026 from September 22 to 24 in Seattle. Save $100 with early-bird pricing until August 8!
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z4n1sb/6767228964/h/eXAL3an</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (0uWEj59btv)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6202602-3593025
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1583298414144679</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 3 Jul 2026 09:21:14 +0000</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Jul 2026 09:24:36 +0000</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 2 Jul 2026 04:17:03 +0000</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (go0BbIMUoR)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6026936-3810853
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-193515716027065</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 1 Jul 2026 16:27:45 +0000</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (hbXn1jQJTV)</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-0881392-7844068
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1565706782398233</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 1 Jul 2026 05:07:37 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 30 Jun 2026 08:53:34 +0000</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (j2cKowrwuw)</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-6586757-6351206
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-510175063560598</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 30 Jun 2026 04:56:23 +0000</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 29 Jun 2026 23:44:37 +0000</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (H7OQM8penQ)</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1191815-3214046
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1161086507307943</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 29 Jun 2026 04:56:45 +0000</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 28 Jun 2026 14:57:16 +0000</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID H7OQM8penQ
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 29, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1724036457613526</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 28 Jun 2026 14:55:52 +0000</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Balance paid on your Amazon seller account</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon Services.
- We have charged your credit card for $81.22 in an attempt to settle your Amazon seller account balance.
- Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
- You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
- You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
- Thank you for selling on Amazon.
- Amazon Services
- Help us improve your experience on selling on Amazon through this brief survey:
- https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202606281349
- Was this email helpful?
- SPC-USAmazon-510175622387886</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 28 Jun 2026 04:47:15 +0000</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 04:59:26 +0000</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 26 Jun 2026 03:07:14 +0000</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (HI24ImSBWG)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-4837972-8437069
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1301823993910502</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 25 Jun 2026 15:41:57 +0000</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID HI24ImSBWG
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 26, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1301823993671780</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 25 Jun 2026 09:07:47 +0000</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF
-Dear Weihai US,
-As a valued Multichannel Fulfilment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than July 2.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_cOSOOyGQjgcTF54?Q_CHL=gl&amp;amp;Q_DL=EMD_7XHD09nVvjxfqAf_cOSOOyGQjgcTF54_CGC_i4S2zEfdL6jRC00&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multichannel Fulfilment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon C</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 25 Jun 2026 04:53:58 +0000</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 25 Jun 2026 00:27:04 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (FyqS0yVk5B)</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 2
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 1
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-3320999-8288160
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1987919249117870</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 24 Jun 2026 04:45:26 +0000</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 23 Jun 2026 15:11:41 +0000</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID FyqS0yVk5B
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 24, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-1671259898541181</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 23 Jun 2026 02:24:45 +0000</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (1M28ecQsao)</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-1410418-0204243
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-404622503407998</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 22 Jun 2026 06:20:20 +0000</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (9U/Ti42WHq)</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-8813600-4095116
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-1671259338897621</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 22 Jun 2026 04:45:03 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 21 Jun 2026 14:27:31 +0000</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID 1M28ecQsao
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 22, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-492583430909528</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 15:35:08 +0000</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (hCxOB8pPpU)</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-0438203-1064657
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-439806876012022</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 15:10:33 +0000</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID hbXn1jQJTV
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 21, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-2163841110748510</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 20 Jun 2026 04:41:46 +0000</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 19 Jun 2026 14:16:06 +0000</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID hCxOB8pPpU
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-193516273769387</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 19 Jun 2026 08:10:33 +0000</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multchannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF
-Dear Weihai US,
-As a valued Multichannel Fulfilment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than July 2.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_cOSOOyGQjgcTF54?Q_CHL=gl&amp;amp;Q_DL=EMD_7XHD09nVvjxfqAf_cOSOOyGQjgcTF54_CGC_i4S2zEfdL6jRC00&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multichannel Fulfilment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon C</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 20:47:57 +0000</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (oWLDk2Qx2d)</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 2
-Quantity Successfully Destroyed: 2
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-8566067-2437751
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1301823991515480</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 20:39:11 +0000</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (Emm3dPMsXA)</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 1
-Quantity Successfully Destroyed: 1
-Quantity Cancelled: 0
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-6737416-2398463
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-1600891154547102</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 17 Jun 2026 17:59:35 +0000</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Please share your feedback on MCF
-Dear Weihai EU,
-As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience. Please complete this survey no later than July 2.
-(button)  Click here to complete survey  https://amazonexteu.qualtrics.com/jfe/form/SV_3LaptS2dCyJQfae?Q_CHL=gl&amp;amp;Q_DL=EMD_G3TZbOh3yA5KUhZ_3LaptS2dCyJQfae_CGC_q2ZHx06yRtKOa12&amp;amp;_g_=g
-This submission form is unique to your Seller account and can only be submitted once.
-DISCLAIMER: Please do not include any Personally Identifiable Information within this survey such as physical addresses, phone numbers, merchant tokens, email addresses, account data, etc.
-Thank you,
-Your Multichannel Fulfillment Team
-This survey is hosted by an external party Qualtrics.com, so the link above does not lead to our website. Your responses are subject to Amazon's Privacy Notice. If you have any concerns about the authenticity of this e-mail or to find out more about Amazon's survey program, please visit the Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 17 Jun 2026 15:48:24 +0000</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID Emm3dPMsXA
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on June 18, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-2040695807881994</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>KYC审核类</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 18 Jun 2026 14:32:29 +0000</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Seller News: June 2026</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services
- 96
- Updates on Prime Day, handling time requirements, Seller Central, and more.
- Our Seller Newsletter provides the most important policy, tool, and program updates from the past month. Stay informed about selling on Amazon.
- Get ready for Prime Day: June 23–26
- Prime Day is back from June 23–26, giving Prime members a head start on the season with deals across top brands they love, trending products, and items exclusive to Amazon. As recently announced, key sourcing dates have been extended, giving you more time to schedule deals, confirm inventory, and plan Prime Exclusive Discounts on eligible selection.
- Read more .
- Updates to improve your product titles begin on July 27
- To ensure your product titles appeal to customers everywhere, we’re making some changes that will help you show your product name and your product highlights seamlessly.
- Read more .
- New handling time requirements for seller-fulfilled products
- Fast and accurate delivery builds customer trust and is a key factor in purchase decisions. In fact, every one day improvement in promised delivery time leads to an average 5% increase in sales. As such, we’re implementing a new handling time requirem</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
